--- a/backend/data/financials_by_company/17V.F.xlsx
+++ b/backend/data/financials_by_company/17V.F.xlsx
@@ -667,580 +667,580 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>-405250</v>
+        <v>-227430</v>
       </c>
       <c r="C2" t="n">
-        <v>0.25</v>
+        <v>0.19</v>
       </c>
       <c r="D2" t="n">
-        <v>5942000</v>
+        <v>6359000</v>
       </c>
       <c r="E2" t="n">
-        <v>-1621000</v>
+        <v>-1197000</v>
       </c>
       <c r="F2" t="n">
-        <v>-1621000</v>
+        <v>-1197000</v>
       </c>
       <c r="G2" t="n">
-        <v>-27000</v>
+        <v>2402000</v>
       </c>
       <c r="H2" t="n">
-        <v>2806000</v>
+        <v>3702000</v>
       </c>
       <c r="I2" t="n">
-        <v>14407000</v>
+        <v>19804000</v>
       </c>
       <c r="J2" t="n">
-        <v>4321000</v>
+        <v>5162000</v>
       </c>
       <c r="K2" t="n">
-        <v>1515000</v>
+        <v>1460000</v>
       </c>
       <c r="L2" t="n">
-        <v>-1496000</v>
+        <v>-425000</v>
       </c>
       <c r="M2" t="n">
-        <v>1496000</v>
-      </c>
-      <c r="N2" t="inlineStr"/>
+        <v>514000</v>
+      </c>
+      <c r="N2" t="n">
+        <v>89000</v>
+      </c>
       <c r="O2" t="n">
-        <v>1188750</v>
+        <v>3371570</v>
       </c>
       <c r="P2" t="n">
-        <v>-314000</v>
+        <v>2402000</v>
       </c>
       <c r="Q2" t="n">
-        <v>23457000</v>
+        <v>30194000</v>
       </c>
       <c r="R2" t="n">
-        <v>3136000</v>
+        <v>1371000</v>
       </c>
       <c r="S2" t="n">
-        <v>137296327</v>
+        <v>133819347</v>
       </c>
       <c r="T2" t="n">
-        <v>126720281</v>
+        <v>125831530</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.0025</v>
+        <v>0.0179</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.0025</v>
+        <v>0.0191</v>
       </c>
       <c r="W2" t="n">
-        <v>-314000</v>
+        <v>2402000</v>
       </c>
       <c r="X2" t="n">
-        <v>-314000</v>
+        <v>2402000</v>
       </c>
       <c r="Y2" t="n">
         <v>0</v>
       </c>
       <c r="Z2" t="n">
-        <v>-314000</v>
+        <v>2402000</v>
       </c>
       <c r="AA2" t="n">
-        <v>-314000</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>-287000</v>
-      </c>
+        <v>2402000</v>
+      </c>
+      <c r="AB2" t="inlineStr"/>
       <c r="AC2" t="n">
-        <v>-27000</v>
+        <v>2402000</v>
       </c>
       <c r="AD2" t="n">
-        <v>46000</v>
+        <v>-1456000</v>
       </c>
       <c r="AE2" t="n">
-        <v>19000</v>
+        <v>946000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-1621000</v>
+        <v>-1197000</v>
       </c>
       <c r="AG2" t="n">
-        <v>286000</v>
-      </c>
-      <c r="AH2" t="inlineStr"/>
+        <v>106000</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>-134000</v>
+      </c>
       <c r="AI2" t="n">
-        <v>1335000</v>
+        <v>1331000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>-1496000</v>
+        <v>-425000</v>
       </c>
       <c r="AK2" t="n">
-        <v>1496000</v>
-      </c>
-      <c r="AL2" t="inlineStr"/>
+        <v>514000</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>89000</v>
+      </c>
       <c r="AM2" t="n">
-        <v>3136000</v>
+        <v>2568000</v>
       </c>
       <c r="AN2" t="n">
-        <v>9050000</v>
+        <v>10390000</v>
       </c>
       <c r="AO2" t="n">
-        <v>6071000</v>
+        <v>8441000</v>
       </c>
       <c r="AP2" t="n">
-        <v>2806000</v>
+        <v>2287000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2447000</v>
+        <v>2287000</v>
       </c>
       <c r="AR2" t="n">
-        <v>359000</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>176000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
-        <v>12186000</v>
+        <v>12958000</v>
       </c>
       <c r="AU2" t="n">
-        <v>14407000</v>
+        <v>19804000</v>
       </c>
       <c r="AV2" t="n">
-        <v>26593000</v>
+        <v>32762000</v>
       </c>
       <c r="AW2" t="n">
-        <v>26593000</v>
+        <v>32762000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>-121410</v>
+        <v>-289274.787535</v>
       </c>
       <c r="C3" t="n">
-        <v>0.19</v>
+        <v>0.263456</v>
       </c>
       <c r="D3" t="n">
-        <v>4712000</v>
+        <v>8711000</v>
       </c>
       <c r="E3" t="n">
-        <v>-639000</v>
+        <v>-1098000</v>
       </c>
       <c r="F3" t="n">
-        <v>-639000</v>
+        <v>-1098000</v>
       </c>
       <c r="G3" t="n">
-        <v>-2000</v>
+        <v>520000</v>
       </c>
       <c r="H3" t="n">
-        <v>2672000</v>
+        <v>5385000</v>
       </c>
       <c r="I3" t="n">
-        <v>13072000</v>
+        <v>26315000</v>
       </c>
       <c r="J3" t="n">
-        <v>4073000</v>
+        <v>7613000</v>
       </c>
       <c r="K3" t="n">
-        <v>1401000</v>
+        <v>2228000</v>
       </c>
       <c r="L3" t="n">
-        <v>-1872000</v>
+        <v>-1521000</v>
       </c>
       <c r="M3" t="n">
-        <v>1872000</v>
+        <v>1522000</v>
       </c>
       <c r="N3" t="n">
-        <v>15000</v>
+        <v>1000</v>
       </c>
       <c r="O3" t="n">
-        <v>515590</v>
+        <v>1328725.212465</v>
       </c>
       <c r="P3" t="n">
-        <v>921000</v>
+        <v>520000</v>
       </c>
       <c r="Q3" t="n">
-        <v>20325000</v>
+        <v>40655000</v>
       </c>
       <c r="R3" t="n">
-        <v>2040000</v>
+        <v>2227000</v>
       </c>
       <c r="S3" t="n">
-        <v>133635025</v>
+        <v>133393929</v>
       </c>
       <c r="T3" t="n">
-        <v>126498197</v>
+        <v>126257101</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0068</v>
+        <v>0.0039</v>
       </c>
       <c r="V3" t="n">
-        <v>0.0073</v>
+        <v>0.0041</v>
       </c>
       <c r="W3" t="n">
-        <v>921000</v>
+        <v>520000</v>
       </c>
       <c r="X3" t="n">
-        <v>921000</v>
+        <v>520000</v>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
       <c r="Z3" t="n">
-        <v>921000</v>
+        <v>520000</v>
       </c>
       <c r="AA3" t="n">
-        <v>921000</v>
-      </c>
-      <c r="AB3" t="n">
-        <v>923000</v>
-      </c>
+        <v>520000</v>
+      </c>
+      <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>-2000</v>
+        <v>520000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-469000</v>
+        <v>186000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-471000</v>
+        <v>706000</v>
       </c>
       <c r="AF3" t="n">
-        <v>-639000</v>
+        <v>-1098000</v>
       </c>
       <c r="AG3" t="inlineStr"/>
       <c r="AH3" t="n">
-        <v>-101000</v>
+        <v>-180000</v>
       </c>
       <c r="AI3" t="n">
-        <v>639000</v>
+        <v>1278000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>-1872000</v>
+        <v>-1521000</v>
       </c>
       <c r="AK3" t="n">
-        <v>1872000</v>
+        <v>1522000</v>
       </c>
       <c r="AL3" t="n">
-        <v>15000</v>
+        <v>1000</v>
       </c>
       <c r="AM3" t="n">
-        <v>2040000</v>
+        <v>3325000</v>
       </c>
       <c r="AN3" t="n">
-        <v>7253000</v>
+        <v>14340000</v>
       </c>
       <c r="AO3" t="n">
-        <v>4615000</v>
+        <v>10927000</v>
       </c>
       <c r="AP3" t="n">
-        <v>2672000</v>
+        <v>3564000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2471000</v>
+        <v>3564000</v>
       </c>
       <c r="AR3" t="n">
-        <v>201000</v>
-      </c>
-      <c r="AS3" t="n">
-        <v>5000</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
-        <v>9293000</v>
+        <v>17665000</v>
       </c>
       <c r="AU3" t="n">
-        <v>13072000</v>
+        <v>26315000</v>
       </c>
       <c r="AV3" t="n">
-        <v>22365000</v>
+        <v>43980000</v>
       </c>
       <c r="AW3" t="n">
-        <v>22365000</v>
+        <v>43980000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>-289274.787535</v>
+        <v>-121410</v>
       </c>
       <c r="C4" t="n">
-        <v>0.263456</v>
+        <v>0.19</v>
       </c>
       <c r="D4" t="n">
-        <v>8711000</v>
+        <v>4712000</v>
       </c>
       <c r="E4" t="n">
-        <v>-1098000</v>
+        <v>-639000</v>
       </c>
       <c r="F4" t="n">
-        <v>-1098000</v>
+        <v>-639000</v>
       </c>
       <c r="G4" t="n">
-        <v>520000</v>
+        <v>-2000</v>
       </c>
       <c r="H4" t="n">
-        <v>5385000</v>
+        <v>2672000</v>
       </c>
       <c r="I4" t="n">
-        <v>26315000</v>
+        <v>13072000</v>
       </c>
       <c r="J4" t="n">
-        <v>7613000</v>
+        <v>4073000</v>
       </c>
       <c r="K4" t="n">
-        <v>2228000</v>
+        <v>1401000</v>
       </c>
       <c r="L4" t="n">
-        <v>-1521000</v>
+        <v>-1872000</v>
       </c>
       <c r="M4" t="n">
-        <v>1522000</v>
+        <v>1872000</v>
       </c>
       <c r="N4" t="n">
-        <v>1000</v>
+        <v>15000</v>
       </c>
       <c r="O4" t="n">
-        <v>1328725.212465</v>
+        <v>515590</v>
       </c>
       <c r="P4" t="n">
-        <v>520000</v>
+        <v>921000</v>
       </c>
       <c r="Q4" t="n">
-        <v>40655000</v>
+        <v>20325000</v>
       </c>
       <c r="R4" t="n">
-        <v>2227000</v>
+        <v>2040000</v>
       </c>
       <c r="S4" t="n">
-        <v>133393929</v>
+        <v>133635025</v>
       </c>
       <c r="T4" t="n">
-        <v>126257101</v>
+        <v>126498197</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0039</v>
+        <v>0.0068</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0041</v>
+        <v>0.0073</v>
       </c>
       <c r="W4" t="n">
-        <v>520000</v>
+        <v>921000</v>
       </c>
       <c r="X4" t="n">
-        <v>520000</v>
+        <v>921000</v>
       </c>
       <c r="Y4" t="n">
         <v>0</v>
       </c>
       <c r="Z4" t="n">
-        <v>520000</v>
+        <v>921000</v>
       </c>
       <c r="AA4" t="n">
-        <v>520000</v>
-      </c>
-      <c r="AB4" t="inlineStr"/>
+        <v>921000</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>923000</v>
+      </c>
       <c r="AC4" t="n">
-        <v>520000</v>
+        <v>-2000</v>
       </c>
       <c r="AD4" t="n">
-        <v>186000</v>
+        <v>-469000</v>
       </c>
       <c r="AE4" t="n">
-        <v>706000</v>
+        <v>-471000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-1098000</v>
+        <v>-639000</v>
       </c>
       <c r="AG4" t="inlineStr"/>
       <c r="AH4" t="n">
-        <v>-180000</v>
+        <v>-101000</v>
       </c>
       <c r="AI4" t="n">
-        <v>1278000</v>
+        <v>639000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>-1521000</v>
+        <v>-1872000</v>
       </c>
       <c r="AK4" t="n">
-        <v>1522000</v>
+        <v>1872000</v>
       </c>
       <c r="AL4" t="n">
-        <v>1000</v>
+        <v>15000</v>
       </c>
       <c r="AM4" t="n">
-        <v>3325000</v>
+        <v>2040000</v>
       </c>
       <c r="AN4" t="n">
-        <v>14340000</v>
+        <v>7253000</v>
       </c>
       <c r="AO4" t="n">
-        <v>10927000</v>
+        <v>4615000</v>
       </c>
       <c r="AP4" t="n">
-        <v>3564000</v>
+        <v>2672000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>3564000</v>
+        <v>2471000</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS4" t="inlineStr"/>
+        <v>201000</v>
+      </c>
+      <c r="AS4" t="n">
+        <v>5000</v>
+      </c>
       <c r="AT4" t="n">
-        <v>17665000</v>
+        <v>9293000</v>
       </c>
       <c r="AU4" t="n">
-        <v>26315000</v>
+        <v>13072000</v>
       </c>
       <c r="AV4" t="n">
-        <v>43980000</v>
+        <v>22365000</v>
       </c>
       <c r="AW4" t="n">
-        <v>43980000</v>
+        <v>22365000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-227430</v>
+        <v>-405250</v>
       </c>
       <c r="C5" t="n">
-        <v>0.19</v>
+        <v>0.25</v>
       </c>
       <c r="D5" t="n">
-        <v>6359000</v>
+        <v>5942000</v>
       </c>
       <c r="E5" t="n">
-        <v>-1197000</v>
+        <v>-1621000</v>
       </c>
       <c r="F5" t="n">
-        <v>-1197000</v>
+        <v>-1621000</v>
       </c>
       <c r="G5" t="n">
-        <v>2402000</v>
+        <v>-27000</v>
       </c>
       <c r="H5" t="n">
-        <v>3702000</v>
+        <v>2806000</v>
       </c>
       <c r="I5" t="n">
-        <v>19804000</v>
+        <v>14407000</v>
       </c>
       <c r="J5" t="n">
-        <v>5162000</v>
+        <v>4321000</v>
       </c>
       <c r="K5" t="n">
-        <v>1460000</v>
+        <v>1515000</v>
       </c>
       <c r="L5" t="n">
-        <v>-425000</v>
+        <v>-1496000</v>
       </c>
       <c r="M5" t="n">
-        <v>514000</v>
-      </c>
-      <c r="N5" t="n">
-        <v>89000</v>
-      </c>
+        <v>1496000</v>
+      </c>
+      <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>3371570</v>
+        <v>1188750</v>
       </c>
       <c r="P5" t="n">
-        <v>2402000</v>
+        <v>-314000</v>
       </c>
       <c r="Q5" t="n">
-        <v>30194000</v>
+        <v>23457000</v>
       </c>
       <c r="R5" t="n">
-        <v>1371000</v>
+        <v>3136000</v>
       </c>
       <c r="S5" t="n">
-        <v>133819347</v>
+        <v>137296327</v>
       </c>
       <c r="T5" t="n">
-        <v>125831530</v>
+        <v>126720281</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0179</v>
+        <v>-0.0025</v>
       </c>
       <c r="V5" t="n">
-        <v>0.0191</v>
+        <v>-0.0025</v>
       </c>
       <c r="W5" t="n">
-        <v>2402000</v>
+        <v>-314000</v>
       </c>
       <c r="X5" t="n">
-        <v>2402000</v>
+        <v>-314000</v>
       </c>
       <c r="Y5" t="n">
         <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>2402000</v>
+        <v>-314000</v>
       </c>
       <c r="AA5" t="n">
-        <v>2402000</v>
-      </c>
-      <c r="AB5" t="inlineStr"/>
+        <v>-314000</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>-287000</v>
+      </c>
       <c r="AC5" t="n">
-        <v>2402000</v>
+        <v>-27000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-1456000</v>
+        <v>46000</v>
       </c>
       <c r="AE5" t="n">
-        <v>946000</v>
+        <v>19000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-1197000</v>
+        <v>-1621000</v>
       </c>
       <c r="AG5" t="n">
-        <v>106000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>-134000</v>
-      </c>
+        <v>286000</v>
+      </c>
+      <c r="AH5" t="inlineStr"/>
       <c r="AI5" t="n">
-        <v>1331000</v>
+        <v>1335000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>-425000</v>
+        <v>-1496000</v>
       </c>
       <c r="AK5" t="n">
-        <v>514000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>89000</v>
-      </c>
+        <v>1496000</v>
+      </c>
+      <c r="AL5" t="inlineStr"/>
       <c r="AM5" t="n">
-        <v>2568000</v>
+        <v>3136000</v>
       </c>
       <c r="AN5" t="n">
-        <v>10390000</v>
+        <v>9050000</v>
       </c>
       <c r="AO5" t="n">
-        <v>8441000</v>
+        <v>6071000</v>
       </c>
       <c r="AP5" t="n">
-        <v>2287000</v>
+        <v>2806000</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2287000</v>
+        <v>2447000</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS5" t="inlineStr"/>
+        <v>359000</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>176000</v>
+      </c>
       <c r="AT5" t="n">
-        <v>12958000</v>
+        <v>12186000</v>
       </c>
       <c r="AU5" t="n">
-        <v>19804000</v>
+        <v>14407000</v>
       </c>
       <c r="AV5" t="n">
-        <v>32762000</v>
+        <v>26593000</v>
       </c>
       <c r="AW5" t="n">
-        <v>32762000</v>
+        <v>26593000</v>
       </c>
     </row>
   </sheetData>
@@ -1536,175 +1536,175 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>127052312</v>
+        <v>125831530</v>
       </c>
       <c r="C2" t="n">
-        <v>127052312</v>
+        <v>125831530</v>
       </c>
       <c r="D2" t="n">
-        <v>20074000</v>
+        <v>3248000</v>
       </c>
       <c r="E2" t="n">
-        <v>23860000</v>
+        <v>12729000</v>
       </c>
       <c r="F2" t="n">
-        <v>26796000</v>
+        <v>8085000</v>
       </c>
       <c r="G2" t="n">
-        <v>98538000</v>
+        <v>81647000</v>
       </c>
       <c r="H2" t="n">
-        <v>52553000</v>
+        <v>15941000</v>
       </c>
       <c r="I2" t="n">
-        <v>26796000</v>
+        <v>8085000</v>
       </c>
       <c r="J2" t="n">
-        <v>733000</v>
+        <v>4246000</v>
       </c>
       <c r="K2" t="n">
-        <v>75411000</v>
+        <v>73164000</v>
       </c>
       <c r="L2" t="n">
-        <v>97193000</v>
+        <v>81647000</v>
       </c>
       <c r="M2" t="n">
-        <v>75411000</v>
+        <v>73164000</v>
       </c>
       <c r="N2" t="n">
-        <v>75411000</v>
+        <v>73164000</v>
       </c>
       <c r="O2" t="n">
-        <v>1225000</v>
+        <v>856000</v>
       </c>
       <c r="P2" t="n">
-        <v>43000</v>
+        <v>-1349000</v>
       </c>
       <c r="Q2" t="n">
-        <v>65960000</v>
+        <v>65738000</v>
       </c>
       <c r="R2" t="n">
-        <v>381000</v>
+        <v>377000</v>
       </c>
       <c r="S2" t="n">
-        <v>381000</v>
+        <v>377000</v>
       </c>
       <c r="T2" t="n">
-        <v>49076000</v>
+        <v>30467000</v>
       </c>
       <c r="U2" t="n">
-        <v>29813000</v>
+        <v>19942000</v>
       </c>
       <c r="V2" t="n">
+        <v>1236000</v>
+      </c>
+      <c r="W2" t="n">
+        <v>6597000</v>
+      </c>
+      <c r="X2" t="n">
+        <v>12109000</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>3626000</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>8483000</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>10525000</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>2397000</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>620000</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>620000</v>
+      </c>
+      <c r="AE2" t="n">
         <v>0</v>
       </c>
-      <c r="W2" t="n">
-        <v>7613000</v>
-      </c>
-      <c r="X2" t="n">
-        <v>22200000</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>418000</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>21782000</v>
-      </c>
-      <c r="AA2" t="n">
-        <v>19263000</v>
-      </c>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="n">
-        <v>1660000</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>315000</v>
-      </c>
-      <c r="AE2" t="n">
-        <v>1345000</v>
-      </c>
       <c r="AF2" t="n">
-        <v>3844000</v>
+        <v>5708000</v>
       </c>
       <c r="AG2" t="n">
-        <v>85000</v>
+        <v>236000</v>
       </c>
       <c r="AH2" t="n">
-        <v>1029000</v>
+        <v>1164000</v>
       </c>
       <c r="AI2" t="n">
-        <v>2730000</v>
+        <v>4308000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>124487000</v>
+        <v>103631000</v>
       </c>
       <c r="AK2" t="n">
-        <v>52671000</v>
+        <v>77165000</v>
       </c>
       <c r="AL2" t="n">
-        <v>3287000</v>
+        <v>2349000</v>
       </c>
       <c r="AM2" t="n">
-        <v>48615000</v>
+        <v>65079000</v>
       </c>
       <c r="AN2" t="n">
-        <v>33228000</v>
+        <v>29596000</v>
       </c>
       <c r="AO2" t="n">
-        <v>15387000</v>
+        <v>35483000</v>
       </c>
       <c r="AP2" t="n">
-        <v>769000</v>
+        <v>9737000</v>
       </c>
       <c r="AQ2" t="n">
-        <v>-461000</v>
+        <v>-4461000</v>
       </c>
       <c r="AR2" t="n">
-        <v>1230000</v>
+        <v>14198000</v>
       </c>
       <c r="AS2" t="n">
-        <v>1185000</v>
+        <v>6994000</v>
       </c>
       <c r="AT2" t="n">
-        <v>45000</v>
+        <v>5739000</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>1465000</v>
       </c>
       <c r="AV2" t="n">
-        <v>71816000</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>52856000</v>
-      </c>
+        <v>26466000</v>
+      </c>
+      <c r="AW2" t="inlineStr"/>
       <c r="AX2" t="n">
-        <v>5075000</v>
+        <v>9019000</v>
       </c>
       <c r="AY2" t="n">
-        <v>5075000</v>
+        <v>3798000</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>5221000</v>
       </c>
       <c r="BA2" t="n">
-        <v>639000</v>
+        <v>1562000</v>
       </c>
       <c r="BB2" t="n">
-        <v>10193000</v>
+        <v>10650000</v>
       </c>
       <c r="BC2" t="n">
-        <v>3053000</v>
+        <v>5235000</v>
       </c>
       <c r="BD2" t="n">
-        <v>3053000</v>
+        <v>5235000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
         <v>126498197</v>
@@ -1713,43 +1713,43 @@
         <v>126498197</v>
       </c>
       <c r="D3" t="n">
-        <v>13676000</v>
+        <v>16644000</v>
       </c>
       <c r="E3" t="n">
-        <v>24392000</v>
+        <v>26846000</v>
       </c>
       <c r="F3" t="n">
-        <v>1642000</v>
+        <v>-3035000</v>
       </c>
       <c r="G3" t="n">
-        <v>95552000</v>
+        <v>97934000</v>
       </c>
       <c r="H3" t="n">
-        <v>2482000</v>
+        <v>17579000</v>
       </c>
       <c r="I3" t="n">
-        <v>1642000</v>
+        <v>-3035000</v>
       </c>
       <c r="J3" t="n">
-        <v>5094000</v>
+        <v>4571000</v>
       </c>
       <c r="K3" t="n">
-        <v>76254000</v>
+        <v>75659000</v>
       </c>
       <c r="L3" t="n">
-        <v>76254000</v>
+        <v>94987000</v>
       </c>
       <c r="M3" t="n">
-        <v>76254000</v>
+        <v>75659000</v>
       </c>
       <c r="N3" t="n">
-        <v>76254000</v>
+        <v>75659000</v>
       </c>
       <c r="O3" t="n">
-        <v>1034000</v>
+        <v>812000</v>
       </c>
       <c r="P3" t="n">
-        <v>211000</v>
+        <v>-713000</v>
       </c>
       <c r="Q3" t="n">
         <v>65960000</v>
@@ -1761,118 +1761,116 @@
         <v>379000</v>
       </c>
       <c r="T3" t="n">
-        <v>43241000</v>
+        <v>49630000</v>
       </c>
       <c r="U3" t="n">
-        <v>13564000</v>
+        <v>33147000</v>
       </c>
       <c r="V3" t="n">
-        <v>1544000</v>
+        <v>1461000</v>
       </c>
       <c r="W3" t="n">
-        <v>7970000</v>
+        <v>8707000</v>
       </c>
       <c r="X3" t="n">
-        <v>4050000</v>
+        <v>22979000</v>
       </c>
       <c r="Y3" t="n">
-        <v>4050000</v>
+        <v>3651000</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>19328000</v>
       </c>
       <c r="AA3" t="n">
-        <v>29677000</v>
+        <v>16483000</v>
       </c>
       <c r="AB3" t="inlineStr"/>
       <c r="AC3" t="n">
-        <v>20342000</v>
+        <v>3867000</v>
       </c>
       <c r="AD3" t="n">
-        <v>1044000</v>
+        <v>920000</v>
       </c>
       <c r="AE3" t="n">
-        <v>19298000</v>
+        <v>2947000</v>
       </c>
       <c r="AF3" t="n">
-        <v>7374000</v>
+        <v>9640000</v>
       </c>
       <c r="AG3" t="n">
-        <v>217000</v>
+        <v>277000</v>
       </c>
       <c r="AH3" t="n">
-        <v>1361000</v>
+        <v>1971000</v>
       </c>
       <c r="AI3" t="n">
-        <v>5796000</v>
+        <v>7392000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>119495000</v>
+        <v>125289000</v>
       </c>
       <c r="AK3" t="n">
-        <v>87336000</v>
+        <v>91227000</v>
       </c>
       <c r="AL3" t="n">
-        <v>2530000</v>
+        <v>2443000</v>
       </c>
       <c r="AM3" t="n">
-        <v>74612000</v>
+        <v>78694000</v>
       </c>
       <c r="AN3" t="n">
-        <v>36027000</v>
+        <v>39042000</v>
       </c>
       <c r="AO3" t="n">
-        <v>38585000</v>
+        <v>39652000</v>
       </c>
       <c r="AP3" t="n">
-        <v>10194000</v>
+        <v>10090000</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-7854000</v>
+        <v>-6097000</v>
       </c>
       <c r="AR3" t="n">
-        <v>18048000</v>
+        <v>16187000</v>
       </c>
       <c r="AS3" t="n">
-        <v>9603000</v>
+        <v>8118000</v>
       </c>
       <c r="AT3" t="n">
-        <v>7023000</v>
+        <v>6639000</v>
       </c>
       <c r="AU3" t="n">
-        <v>1422000</v>
+        <v>1430000</v>
       </c>
       <c r="AV3" t="n">
-        <v>32159000</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>0</v>
-      </c>
+        <v>34062000</v>
+      </c>
+      <c r="AW3" t="inlineStr"/>
       <c r="AX3" t="n">
-        <v>10332000</v>
+        <v>11998000</v>
       </c>
       <c r="AY3" t="n">
-        <v>4957000</v>
+        <v>5116000</v>
       </c>
       <c r="AZ3" t="n">
-        <v>5375000</v>
+        <v>6882000</v>
       </c>
       <c r="BA3" t="n">
-        <v>1627000</v>
+        <v>1606000</v>
       </c>
       <c r="BB3" t="n">
-        <v>14578000</v>
+        <v>14827000</v>
       </c>
       <c r="BC3" t="n">
-        <v>5622000</v>
+        <v>5631000</v>
       </c>
       <c r="BD3" t="n">
-        <v>5622000</v>
+        <v>5631000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
         <v>126498197</v>
@@ -1881,43 +1879,43 @@
         <v>126498197</v>
       </c>
       <c r="D4" t="n">
-        <v>16644000</v>
+        <v>13676000</v>
       </c>
       <c r="E4" t="n">
-        <v>26846000</v>
+        <v>24392000</v>
       </c>
       <c r="F4" t="n">
-        <v>-3035000</v>
+        <v>1642000</v>
       </c>
       <c r="G4" t="n">
-        <v>97934000</v>
+        <v>95552000</v>
       </c>
       <c r="H4" t="n">
-        <v>17579000</v>
+        <v>2482000</v>
       </c>
       <c r="I4" t="n">
-        <v>-3035000</v>
+        <v>1642000</v>
       </c>
       <c r="J4" t="n">
-        <v>4571000</v>
+        <v>5094000</v>
       </c>
       <c r="K4" t="n">
-        <v>75659000</v>
+        <v>76254000</v>
       </c>
       <c r="L4" t="n">
-        <v>94987000</v>
+        <v>76254000</v>
       </c>
       <c r="M4" t="n">
-        <v>75659000</v>
+        <v>76254000</v>
       </c>
       <c r="N4" t="n">
-        <v>75659000</v>
+        <v>76254000</v>
       </c>
       <c r="O4" t="n">
-        <v>812000</v>
+        <v>1034000</v>
       </c>
       <c r="P4" t="n">
-        <v>-713000</v>
+        <v>211000</v>
       </c>
       <c r="Q4" t="n">
         <v>65960000</v>
@@ -1929,279 +1927,281 @@
         <v>379000</v>
       </c>
       <c r="T4" t="n">
-        <v>49630000</v>
+        <v>43241000</v>
       </c>
       <c r="U4" t="n">
-        <v>33147000</v>
+        <v>13564000</v>
       </c>
       <c r="V4" t="n">
-        <v>1461000</v>
+        <v>1544000</v>
       </c>
       <c r="W4" t="n">
-        <v>8707000</v>
+        <v>7970000</v>
       </c>
       <c r="X4" t="n">
-        <v>22979000</v>
+        <v>4050000</v>
       </c>
       <c r="Y4" t="n">
-        <v>3651000</v>
+        <v>4050000</v>
       </c>
       <c r="Z4" t="n">
-        <v>19328000</v>
+        <v>0</v>
       </c>
       <c r="AA4" t="n">
-        <v>16483000</v>
+        <v>29677000</v>
       </c>
       <c r="AB4" t="inlineStr"/>
       <c r="AC4" t="n">
-        <v>3867000</v>
+        <v>20342000</v>
       </c>
       <c r="AD4" t="n">
-        <v>920000</v>
+        <v>1044000</v>
       </c>
       <c r="AE4" t="n">
-        <v>2947000</v>
+        <v>19298000</v>
       </c>
       <c r="AF4" t="n">
-        <v>9640000</v>
+        <v>7374000</v>
       </c>
       <c r="AG4" t="n">
-        <v>277000</v>
+        <v>217000</v>
       </c>
       <c r="AH4" t="n">
-        <v>1971000</v>
+        <v>1361000</v>
       </c>
       <c r="AI4" t="n">
-        <v>7392000</v>
+        <v>5796000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>125289000</v>
+        <v>119495000</v>
       </c>
       <c r="AK4" t="n">
-        <v>91227000</v>
+        <v>87336000</v>
       </c>
       <c r="AL4" t="n">
-        <v>2443000</v>
+        <v>2530000</v>
       </c>
       <c r="AM4" t="n">
-        <v>78694000</v>
+        <v>74612000</v>
       </c>
       <c r="AN4" t="n">
-        <v>39042000</v>
+        <v>36027000</v>
       </c>
       <c r="AO4" t="n">
-        <v>39652000</v>
+        <v>38585000</v>
       </c>
       <c r="AP4" t="n">
-        <v>10090000</v>
+        <v>10194000</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-6097000</v>
+        <v>-7854000</v>
       </c>
       <c r="AR4" t="n">
-        <v>16187000</v>
+        <v>18048000</v>
       </c>
       <c r="AS4" t="n">
-        <v>8118000</v>
+        <v>9603000</v>
       </c>
       <c r="AT4" t="n">
-        <v>6639000</v>
+        <v>7023000</v>
       </c>
       <c r="AU4" t="n">
-        <v>1430000</v>
+        <v>1422000</v>
       </c>
       <c r="AV4" t="n">
-        <v>34062000</v>
-      </c>
-      <c r="AW4" t="inlineStr"/>
+        <v>32159000</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
       <c r="AX4" t="n">
-        <v>11998000</v>
+        <v>10332000</v>
       </c>
       <c r="AY4" t="n">
-        <v>5116000</v>
+        <v>4957000</v>
       </c>
       <c r="AZ4" t="n">
-        <v>6882000</v>
+        <v>5375000</v>
       </c>
       <c r="BA4" t="n">
-        <v>1606000</v>
+        <v>1627000</v>
       </c>
       <c r="BB4" t="n">
-        <v>14827000</v>
+        <v>14578000</v>
       </c>
       <c r="BC4" t="n">
-        <v>5631000</v>
+        <v>5622000</v>
       </c>
       <c r="BD4" t="n">
-        <v>5631000</v>
+        <v>5622000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>125831530</v>
+        <v>127052312</v>
       </c>
       <c r="C5" t="n">
-        <v>125831530</v>
+        <v>127052312</v>
       </c>
       <c r="D5" t="n">
-        <v>3248000</v>
+        <v>20074000</v>
       </c>
       <c r="E5" t="n">
-        <v>12729000</v>
+        <v>23860000</v>
       </c>
       <c r="F5" t="n">
-        <v>8085000</v>
+        <v>26796000</v>
       </c>
       <c r="G5" t="n">
-        <v>81647000</v>
+        <v>98538000</v>
       </c>
       <c r="H5" t="n">
-        <v>15941000</v>
+        <v>52553000</v>
       </c>
       <c r="I5" t="n">
-        <v>8085000</v>
+        <v>26796000</v>
       </c>
       <c r="J5" t="n">
-        <v>4246000</v>
+        <v>733000</v>
       </c>
       <c r="K5" t="n">
-        <v>73164000</v>
+        <v>75411000</v>
       </c>
       <c r="L5" t="n">
-        <v>81647000</v>
+        <v>97193000</v>
       </c>
       <c r="M5" t="n">
-        <v>73164000</v>
+        <v>75411000</v>
       </c>
       <c r="N5" t="n">
-        <v>73164000</v>
+        <v>75411000</v>
       </c>
       <c r="O5" t="n">
-        <v>856000</v>
+        <v>1225000</v>
       </c>
       <c r="P5" t="n">
-        <v>-1349000</v>
+        <v>43000</v>
       </c>
       <c r="Q5" t="n">
-        <v>65738000</v>
+        <v>65960000</v>
       </c>
       <c r="R5" t="n">
-        <v>377000</v>
+        <v>381000</v>
       </c>
       <c r="S5" t="n">
-        <v>377000</v>
+        <v>381000</v>
       </c>
       <c r="T5" t="n">
-        <v>30467000</v>
+        <v>49076000</v>
       </c>
       <c r="U5" t="n">
-        <v>19942000</v>
+        <v>29813000</v>
       </c>
       <c r="V5" t="n">
-        <v>1236000</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>6597000</v>
+        <v>7613000</v>
       </c>
       <c r="X5" t="n">
-        <v>12109000</v>
+        <v>22200000</v>
       </c>
       <c r="Y5" t="n">
-        <v>3626000</v>
+        <v>418000</v>
       </c>
       <c r="Z5" t="n">
-        <v>8483000</v>
+        <v>21782000</v>
       </c>
       <c r="AA5" t="n">
-        <v>10525000</v>
-      </c>
-      <c r="AB5" t="n">
-        <v>2397000</v>
-      </c>
+        <v>19263000</v>
+      </c>
+      <c r="AB5" t="inlineStr"/>
       <c r="AC5" t="n">
-        <v>620000</v>
+        <v>1660000</v>
       </c>
       <c r="AD5" t="n">
-        <v>620000</v>
+        <v>315000</v>
       </c>
       <c r="AE5" t="n">
+        <v>1345000</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>3844000</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>85000</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>1029000</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>2730000</v>
+      </c>
+      <c r="AJ5" t="n">
+        <v>124487000</v>
+      </c>
+      <c r="AK5" t="n">
+        <v>52671000</v>
+      </c>
+      <c r="AL5" t="n">
+        <v>3287000</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>48615000</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>33228000</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>15387000</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>769000</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>-461000</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>1230000</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>1185000</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>45000</v>
+      </c>
+      <c r="AU5" t="n">
         <v>0</v>
       </c>
-      <c r="AF5" t="n">
-        <v>5708000</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>236000</v>
-      </c>
-      <c r="AH5" t="n">
-        <v>1164000</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>4308000</v>
-      </c>
-      <c r="AJ5" t="n">
-        <v>103631000</v>
-      </c>
-      <c r="AK5" t="n">
-        <v>77165000</v>
-      </c>
-      <c r="AL5" t="n">
-        <v>2349000</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>65079000</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>29596000</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>35483000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>9737000</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>-4461000</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>14198000</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>6994000</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>5739000</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>1465000</v>
-      </c>
       <c r="AV5" t="n">
-        <v>26466000</v>
-      </c>
-      <c r="AW5" t="inlineStr"/>
+        <v>71816000</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>52856000</v>
+      </c>
       <c r="AX5" t="n">
-        <v>9019000</v>
+        <v>5075000</v>
       </c>
       <c r="AY5" t="n">
-        <v>3798000</v>
+        <v>5075000</v>
       </c>
       <c r="AZ5" t="n">
-        <v>5221000</v>
+        <v>0</v>
       </c>
       <c r="BA5" t="n">
-        <v>1562000</v>
+        <v>639000</v>
       </c>
       <c r="BB5" t="n">
-        <v>10650000</v>
+        <v>10193000</v>
       </c>
       <c r="BC5" t="n">
-        <v>5235000</v>
+        <v>3053000</v>
       </c>
       <c r="BD5" t="n">
-        <v>5235000</v>
+        <v>3053000</v>
       </c>
     </row>
   </sheetData>
@@ -2417,474 +2417,474 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45657</v>
+        <v>44561</v>
       </c>
       <c r="B2" t="n">
-        <v>8341000</v>
+        <v>-2661000</v>
       </c>
       <c r="C2" t="n">
-        <v>-3300000</v>
+        <v>-13614000</v>
       </c>
       <c r="D2" t="n">
-        <v>9000000</v>
+        <v>16336000</v>
       </c>
       <c r="E2" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>-10000</v>
+        <v>-3262000</v>
       </c>
       <c r="G2" t="n">
-        <v>4319000</v>
+        <v>5235000</v>
       </c>
       <c r="H2" t="n">
-        <v>5622000</v>
+        <v>42095000</v>
       </c>
       <c r="I2" t="n">
-        <v>-139000</v>
+        <v>216000</v>
       </c>
       <c r="J2" t="n">
-        <v>-1164000</v>
+        <v>-37076000</v>
       </c>
       <c r="K2" t="n">
-        <v>1779000</v>
-      </c>
-      <c r="L2" t="n">
-        <v>-1604000</v>
-      </c>
+        <v>1502000</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
-        <v>-2012000</v>
+        <v>-492000</v>
       </c>
       <c r="N2" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="O2" t="n">
-        <v>2000</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>5700000</v>
+        <v>2722000</v>
       </c>
       <c r="Q2" t="n">
-        <v>5700000</v>
+        <v>2722000</v>
       </c>
       <c r="R2" t="n">
-        <v>-3300000</v>
+        <v>-13614000</v>
       </c>
       <c r="S2" t="n">
-        <v>9000000</v>
+        <v>16336000</v>
       </c>
       <c r="T2" t="n">
-        <v>-11294000</v>
-      </c>
-      <c r="U2" t="n">
-        <v>-1804000</v>
-      </c>
+        <v>-39179000</v>
+      </c>
+      <c r="U2" t="inlineStr"/>
       <c r="V2" t="n">
-        <v>-9480000</v>
+        <v>-35917000</v>
       </c>
       <c r="W2" t="n">
-        <v>-9480000</v>
+        <v>-35917000</v>
       </c>
       <c r="X2" t="n">
-        <v>-8000</v>
+        <v>-371000</v>
       </c>
       <c r="Y2" t="n">
-        <v>-8000</v>
+        <v>-371000</v>
       </c>
       <c r="Z2" t="n">
-        <v>-2000</v>
+        <v>-2891000</v>
       </c>
       <c r="AA2" t="n">
-        <v>8351000</v>
+        <v>601000</v>
       </c>
       <c r="AB2" t="n">
-        <v>-657000</v>
+        <v>-1355000</v>
       </c>
       <c r="AC2" t="n">
-        <v>-73000</v>
+        <v>-3179000</v>
       </c>
       <c r="AD2" t="n">
-        <v>2747000</v>
+        <v>-908000</v>
       </c>
       <c r="AE2" t="n">
-        <v>-355000</v>
+        <v>718000</v>
       </c>
       <c r="AF2" t="n">
-        <v>-2465000</v>
+        <v>-2989000</v>
       </c>
       <c r="AG2" t="n">
-        <v>1496000</v>
+        <v>425000</v>
       </c>
       <c r="AH2" t="n">
-        <v>232000</v>
+        <v>196000</v>
       </c>
       <c r="AI2" t="n">
-        <v>2806000</v>
+        <v>3702000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>2447000</v>
+        <v>2287000</v>
       </c>
       <c r="AK2" t="n">
-        <v>359000</v>
+        <v>1415000</v>
       </c>
       <c r="AL2" t="inlineStr"/>
-      <c r="AM2" t="n">
-        <v>158000</v>
-      </c>
+      <c r="AM2" t="inlineStr"/>
       <c r="AN2" t="n">
-        <v>19000</v>
+        <v>946000</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45291</v>
+        <v>44926</v>
       </c>
       <c r="B3" t="n">
-        <v>7986000</v>
+        <v>1360000</v>
       </c>
       <c r="C3" t="n">
-        <v>-3581000</v>
+        <v>-6728000</v>
       </c>
       <c r="D3" t="n">
-        <v>2553000</v>
+        <v>14985000</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>224000</v>
       </c>
       <c r="F3" t="n">
-        <v>-234000</v>
+        <v>-4206000</v>
       </c>
       <c r="G3" t="n">
-        <v>5622000</v>
+        <v>5631000</v>
       </c>
       <c r="H3" t="n">
-        <v>5631000</v>
+        <v>5235000</v>
       </c>
       <c r="I3" t="n">
-        <v>-83000</v>
+        <v>-404000</v>
       </c>
       <c r="J3" t="n">
-        <v>74000</v>
+        <v>800000</v>
       </c>
       <c r="K3" t="n">
-        <v>-2806000</v>
-      </c>
-      <c r="L3" t="n">
-        <v>-342000</v>
-      </c>
+        <v>6922000</v>
+      </c>
+      <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
-        <v>-1259000</v>
+        <v>-637000</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>224000</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>224000</v>
       </c>
       <c r="P3" t="n">
-        <v>-1028000</v>
+        <v>8257000</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1028000</v>
+        <v>8257000</v>
       </c>
       <c r="R3" t="n">
-        <v>-3581000</v>
+        <v>-6728000</v>
       </c>
       <c r="S3" t="n">
-        <v>2553000</v>
+        <v>14985000</v>
       </c>
       <c r="T3" t="n">
-        <v>-5340000</v>
-      </c>
-      <c r="U3" t="n">
-        <v>-2173000</v>
-      </c>
+        <v>-11688000</v>
+      </c>
+      <c r="U3" t="inlineStr"/>
       <c r="V3" t="n">
-        <v>-2933000</v>
+        <v>-7482000</v>
       </c>
       <c r="W3" t="n">
-        <v>-2933000</v>
+        <v>-7482000</v>
       </c>
       <c r="X3" t="n">
-        <v>-33000</v>
+        <v>-860000</v>
       </c>
       <c r="Y3" t="n">
-        <v>-33000</v>
+        <v>-860000</v>
       </c>
       <c r="Z3" t="n">
-        <v>-201000</v>
+        <v>-3346000</v>
       </c>
       <c r="AA3" t="n">
-        <v>8220000</v>
+        <v>5566000</v>
       </c>
       <c r="AB3" t="n">
-        <v>-336000</v>
+        <v>-621000</v>
       </c>
       <c r="AC3" t="n">
-        <v>-1073000</v>
+        <v>-1357000</v>
       </c>
       <c r="AD3" t="n">
-        <v>-790000</v>
+        <v>3489000</v>
       </c>
       <c r="AE3" t="n">
-        <v>-682000</v>
+        <v>-2329000</v>
       </c>
       <c r="AF3" t="n">
-        <v>399000</v>
+        <v>-2517000</v>
       </c>
       <c r="AG3" t="n">
-        <v>1872000</v>
+        <v>1521000</v>
       </c>
       <c r="AH3" t="n">
-        <v>183000</v>
+        <v>72000</v>
       </c>
       <c r="AI3" t="n">
-        <v>2672000</v>
+        <v>5385000</v>
       </c>
       <c r="AJ3" t="n">
-        <v>2471000</v>
+        <v>3564000</v>
       </c>
       <c r="AK3" t="n">
-        <v>201000</v>
-      </c>
-      <c r="AL3" t="inlineStr"/>
+        <v>1821000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>40000</v>
+      </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>40000</v>
       </c>
       <c r="AN3" t="n">
-        <v>-471000</v>
+        <v>706000</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44926</v>
+        <v>45291</v>
       </c>
       <c r="B4" t="n">
-        <v>1360000</v>
+        <v>7986000</v>
       </c>
       <c r="C4" t="n">
-        <v>-6728000</v>
+        <v>-3581000</v>
       </c>
       <c r="D4" t="n">
-        <v>14985000</v>
+        <v>2553000</v>
       </c>
       <c r="E4" t="n">
-        <v>224000</v>
+        <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>-4206000</v>
+        <v>-234000</v>
       </c>
       <c r="G4" t="n">
+        <v>5622000</v>
+      </c>
+      <c r="H4" t="n">
         <v>5631000</v>
       </c>
-      <c r="H4" t="n">
-        <v>5235000</v>
-      </c>
       <c r="I4" t="n">
-        <v>-404000</v>
+        <v>-83000</v>
       </c>
       <c r="J4" t="n">
-        <v>800000</v>
+        <v>74000</v>
       </c>
       <c r="K4" t="n">
-        <v>6922000</v>
-      </c>
-      <c r="L4" t="inlineStr"/>
+        <v>-2806000</v>
+      </c>
+      <c r="L4" t="n">
+        <v>-342000</v>
+      </c>
       <c r="M4" t="n">
-        <v>-637000</v>
+        <v>-1259000</v>
       </c>
       <c r="N4" t="n">
-        <v>224000</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>224000</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>8257000</v>
+        <v>-1028000</v>
       </c>
       <c r="Q4" t="n">
-        <v>8257000</v>
+        <v>-1028000</v>
       </c>
       <c r="R4" t="n">
-        <v>-6728000</v>
+        <v>-3581000</v>
       </c>
       <c r="S4" t="n">
-        <v>14985000</v>
+        <v>2553000</v>
       </c>
       <c r="T4" t="n">
-        <v>-11688000</v>
-      </c>
-      <c r="U4" t="inlineStr"/>
+        <v>-5340000</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-2173000</v>
+      </c>
       <c r="V4" t="n">
-        <v>-7482000</v>
+        <v>-2933000</v>
       </c>
       <c r="W4" t="n">
-        <v>-7482000</v>
+        <v>-2933000</v>
       </c>
       <c r="X4" t="n">
-        <v>-860000</v>
+        <v>-33000</v>
       </c>
       <c r="Y4" t="n">
-        <v>-860000</v>
+        <v>-33000</v>
       </c>
       <c r="Z4" t="n">
-        <v>-3346000</v>
+        <v>-201000</v>
       </c>
       <c r="AA4" t="n">
-        <v>5566000</v>
+        <v>8220000</v>
       </c>
       <c r="AB4" t="n">
-        <v>-621000</v>
+        <v>-336000</v>
       </c>
       <c r="AC4" t="n">
-        <v>-1357000</v>
+        <v>-1073000</v>
       </c>
       <c r="AD4" t="n">
-        <v>3489000</v>
+        <v>-790000</v>
       </c>
       <c r="AE4" t="n">
-        <v>-2329000</v>
+        <v>-682000</v>
       </c>
       <c r="AF4" t="n">
-        <v>-2517000</v>
+        <v>399000</v>
       </c>
       <c r="AG4" t="n">
-        <v>1521000</v>
+        <v>1872000</v>
       </c>
       <c r="AH4" t="n">
-        <v>72000</v>
+        <v>183000</v>
       </c>
       <c r="AI4" t="n">
-        <v>5385000</v>
+        <v>2672000</v>
       </c>
       <c r="AJ4" t="n">
-        <v>3564000</v>
+        <v>2471000</v>
       </c>
       <c r="AK4" t="n">
-        <v>1821000</v>
-      </c>
-      <c r="AL4" t="n">
-        <v>40000</v>
-      </c>
+        <v>201000</v>
+      </c>
+      <c r="AL4" t="inlineStr"/>
       <c r="AM4" t="n">
-        <v>40000</v>
+        <v>0</v>
       </c>
       <c r="AN4" t="n">
-        <v>706000</v>
+        <v>-471000</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44561</v>
+        <v>45657</v>
       </c>
       <c r="B5" t="n">
-        <v>-2661000</v>
+        <v>8341000</v>
       </c>
       <c r="C5" t="n">
-        <v>-13614000</v>
+        <v>-3300000</v>
       </c>
       <c r="D5" t="n">
-        <v>16336000</v>
+        <v>9000000</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="F5" t="n">
-        <v>-3262000</v>
+        <v>-10000</v>
       </c>
       <c r="G5" t="n">
-        <v>5235000</v>
+        <v>4319000</v>
       </c>
       <c r="H5" t="n">
-        <v>42095000</v>
+        <v>5622000</v>
       </c>
       <c r="I5" t="n">
-        <v>216000</v>
+        <v>-139000</v>
       </c>
       <c r="J5" t="n">
-        <v>-37076000</v>
+        <v>-1164000</v>
       </c>
       <c r="K5" t="n">
-        <v>1502000</v>
-      </c>
-      <c r="L5" t="inlineStr"/>
+        <v>1779000</v>
+      </c>
+      <c r="L5" t="n">
+        <v>-1604000</v>
+      </c>
       <c r="M5" t="n">
-        <v>-492000</v>
+        <v>-2012000</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>2000</v>
       </c>
       <c r="P5" t="n">
-        <v>2722000</v>
+        <v>5700000</v>
       </c>
       <c r="Q5" t="n">
-        <v>2722000</v>
+        <v>5700000</v>
       </c>
       <c r="R5" t="n">
-        <v>-13614000</v>
+        <v>-3300000</v>
       </c>
       <c r="S5" t="n">
-        <v>16336000</v>
+        <v>9000000</v>
       </c>
       <c r="T5" t="n">
-        <v>-39179000</v>
-      </c>
-      <c r="U5" t="inlineStr"/>
+        <v>-11294000</v>
+      </c>
+      <c r="U5" t="n">
+        <v>-1804000</v>
+      </c>
       <c r="V5" t="n">
-        <v>-35917000</v>
+        <v>-9480000</v>
       </c>
       <c r="W5" t="n">
-        <v>-35917000</v>
+        <v>-9480000</v>
       </c>
       <c r="X5" t="n">
-        <v>-371000</v>
+        <v>-8000</v>
       </c>
       <c r="Y5" t="n">
-        <v>-371000</v>
+        <v>-8000</v>
       </c>
       <c r="Z5" t="n">
-        <v>-2891000</v>
+        <v>-2000</v>
       </c>
       <c r="AA5" t="n">
-        <v>601000</v>
+        <v>8351000</v>
       </c>
       <c r="AB5" t="n">
-        <v>-1355000</v>
+        <v>-657000</v>
       </c>
       <c r="AC5" t="n">
-        <v>-3179000</v>
+        <v>-73000</v>
       </c>
       <c r="AD5" t="n">
-        <v>-908000</v>
+        <v>2747000</v>
       </c>
       <c r="AE5" t="n">
-        <v>718000</v>
+        <v>-355000</v>
       </c>
       <c r="AF5" t="n">
-        <v>-2989000</v>
+        <v>-2465000</v>
       </c>
       <c r="AG5" t="n">
-        <v>425000</v>
+        <v>1496000</v>
       </c>
       <c r="AH5" t="n">
-        <v>196000</v>
+        <v>232000</v>
       </c>
       <c r="AI5" t="n">
-        <v>3702000</v>
+        <v>2806000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>2287000</v>
+        <v>2447000</v>
       </c>
       <c r="AK5" t="n">
-        <v>1415000</v>
+        <v>359000</v>
       </c>
       <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr"/>
+      <c r="AM5" t="n">
+        <v>158000</v>
+      </c>
       <c r="AN5" t="n">
-        <v>946000</v>
+        <v>19000</v>
       </c>
     </row>
   </sheetData>
@@ -3384,197 +3384,197 @@
       </c>
       <c r="CS1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="CT1" t="inlineStr">
+        <is>
+          <t>marketState</t>
+        </is>
+      </c>
+      <c r="CU1" t="inlineStr">
+        <is>
+          <t>regularMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="CV1" t="inlineStr">
+        <is>
+          <t>regularMarketPrice</t>
+        </is>
+      </c>
+      <c r="CW1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="CX1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="CY1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="CZ1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="DA1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="DB1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="DC1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="DD1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="DE1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="DF1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DG1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="DH1" t="inlineStr">
+        <is>
+          <t>hasPrePostMarketData</t>
+        </is>
+      </c>
+      <c r="DI1" t="inlineStr">
+        <is>
+          <t>firstTradeDateMilliseconds</t>
+        </is>
+      </c>
+      <c r="DJ1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="DK1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="DL1" t="inlineStr">
+        <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="CT1" t="inlineStr">
+      <c r="DM1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="CU1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="CV1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="CW1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="CX1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="CY1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="CZ1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="DA1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="DB1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="DC1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="DD1" t="inlineStr">
-        <is>
-          <t>regularMarketChangePercent</t>
-        </is>
-      </c>
-      <c r="DE1" t="inlineStr">
-        <is>
-          <t>regularMarketPrice</t>
-        </is>
-      </c>
-      <c r="DF1" t="inlineStr">
-        <is>
-          <t>marketState</t>
-        </is>
-      </c>
-      <c r="DG1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="DH1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="DI1" t="inlineStr">
+      <c r="DN1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="DJ1" t="inlineStr">
+      <c r="DO1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="DK1" t="inlineStr">
+      <c r="DP1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="DL1" t="inlineStr">
+      <c r="DQ1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="DM1" t="inlineStr">
+      <c r="DR1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="DN1" t="inlineStr">
+      <c r="DS1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="DO1" t="inlineStr">
+      <c r="DT1" t="inlineStr">
         <is>
           <t>earningsTimestampStart</t>
         </is>
       </c>
-      <c r="DP1" t="inlineStr">
+      <c r="DU1" t="inlineStr">
         <is>
           <t>earningsTimestampEnd</t>
         </is>
       </c>
-      <c r="DQ1" t="inlineStr">
+      <c r="DV1" t="inlineStr">
         <is>
           <t>earningsCallTimestampStart</t>
         </is>
       </c>
-      <c r="DR1" t="inlineStr">
+      <c r="DW1" t="inlineStr">
         <is>
           <t>earningsCallTimestampEnd</t>
         </is>
       </c>
-      <c r="DS1" t="inlineStr">
+      <c r="DX1" t="inlineStr">
         <is>
           <t>isEarningsDateEstimate</t>
         </is>
       </c>
-      <c r="DT1" t="inlineStr">
+      <c r="DY1" t="inlineStr">
         <is>
           <t>epsTrailingTwelveMonths</t>
         </is>
       </c>
-      <c r="DU1" t="inlineStr">
+      <c r="DZ1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChange</t>
         </is>
       </c>
-      <c r="DV1" t="inlineStr">
+      <c r="EA1" t="inlineStr">
         <is>
           <t>fiftyDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DW1" t="inlineStr">
+      <c r="EB1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChange</t>
         </is>
       </c>
-      <c r="DX1" t="inlineStr">
+      <c r="EC1" t="inlineStr">
         <is>
           <t>twoHundredDayAverageChangePercent</t>
         </is>
       </c>
-      <c r="DY1" t="inlineStr">
+      <c r="ED1" t="inlineStr">
         <is>
           <t>sourceInterval</t>
         </is>
       </c>
-      <c r="DZ1" t="inlineStr">
+      <c r="EE1" t="inlineStr">
         <is>
           <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="EA1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="EB1" t="inlineStr">
-        <is>
-          <t>hasPrePostMarketData</t>
-        </is>
-      </c>
-      <c r="EC1" t="inlineStr">
-        <is>
-          <t>firstTradeDateMilliseconds</t>
-        </is>
-      </c>
-      <c r="ED1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EE1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
         </is>
       </c>
       <c r="EF1" t="inlineStr">
@@ -3656,7 +3656,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>[{'maxAge': 1, 'name': 'Mr. Jeremy Anthony Philip Randall ACA', 'age': 61, 'title': 'Co-Founder, CEO &amp; Executive Director', 'yearBorn': 1964, 'fiscalYear': 2024, 'totalPay': 454569, 'exercisedValue': 0, 'unexercisedValue': 64197}, {'maxAge': 1, 'name': 'Mr. Daniel James Wells', 'age': 38, 'title': 'CFO &amp; Director', 'yearBorn': 1987, 'fiscalYear': 2024, 'totalPay': 283079, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Peter  Jackson', 'title': 'Chief Digital &amp; Technology Officer', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ben  Colman', 'title': 'Director of Corporate Development', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Katherine Louise Bache', 'age': 44, 'title': 'Chief Marketing &amp; Innovation Officer and Director', 'yearBorn': 1981, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Domenico  Barbaro', 'title': 'Head of Procurement', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ennio  Schiro', 'title': 'Head of ESG Strategy', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Matt  Jeffs', 'title': 'Head of M&amp;A', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Louise  McCarthy', 'title': 'Company Secretary', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
+          <t>[{'maxAge': 1, 'name': 'Mr. Jeremy Anthony Philip Randall ACA', 'age': 61, 'title': 'Co-Founder, CEO &amp; Executive Director', 'yearBorn': 1964, 'fiscalYear': 2024, 'totalPay': 452788, 'exercisedValue': 0, 'unexercisedValue': 63946}, {'maxAge': 1, 'name': 'Mr. Daniel James Wells', 'age': 38, 'title': 'CFO &amp; Director', 'yearBorn': 1987, 'fiscalYear': 2024, 'totalPay': 281970, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Peter  Jackson', 'title': 'Chief Digital &amp; Technology Officer', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ben  Colman', 'title': 'Director of Corporate Development', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Ms. Katherine Louise Bache', 'age': 44, 'title': 'Chief Marketing &amp; Innovation Officer and Director', 'yearBorn': 1981, 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Domenico  Barbaro', 'title': 'Head of Procurement', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Ennio  Schiro', 'title': 'Head of ESG Strategy', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Mr. Matt  Jeffs', 'title': 'Head of M&amp;A', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}, {'maxAge': 1, 'name': 'Louise  McCarthy', 'title': 'Company Secretary', 'fiscalYear': 2024, 'exercisedValue': 0, 'unexercisedValue': 0}]</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -3674,61 +3674,61 @@
         <v>4</v>
       </c>
       <c r="T2" t="n">
-        <v>0.63</v>
+        <v>0.745</v>
       </c>
       <c r="U2" t="n">
-        <v>0.62</v>
+        <v>0.725</v>
       </c>
       <c r="V2" t="n">
-        <v>0.62</v>
+        <v>0.725</v>
       </c>
       <c r="W2" t="n">
-        <v>0.63</v>
+        <v>0.745</v>
       </c>
       <c r="X2" t="n">
-        <v>0.63</v>
+        <v>0.745</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.62</v>
+        <v>0.725</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.62</v>
+        <v>0.725</v>
       </c>
       <c r="AA2" t="n">
-        <v>0.63</v>
+        <v>0.745</v>
       </c>
       <c r="AB2" t="n">
         <v>0</v>
       </c>
       <c r="AC2" t="n">
-        <v>0.239</v>
+        <v>0.226</v>
       </c>
       <c r="AD2" t="n">
-        <v>3100</v>
+        <v>10207</v>
       </c>
       <c r="AE2" t="n">
-        <v>3100</v>
+        <v>10207</v>
       </c>
       <c r="AF2" t="n">
-        <v>75</v>
+        <v>238</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1020</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1020</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.62</v>
+        <v>0.725</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0.72</v>
+        <v>0.845</v>
       </c>
       <c r="AK2" t="n">
-        <v>76751688</v>
+        <v>90482624</v>
       </c>
       <c r="AL2" t="n">
-        <v>79482161</v>
+        <v>92422849</v>
       </c>
       <c r="AM2" t="n">
         <v>0.555</v>
@@ -3743,13 +3743,13 @@
         <v>0.244</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.1824918</v>
+        <v>2.5729413</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.6794</v>
+        <v>0.6798</v>
       </c>
       <c r="AS2" t="n">
-        <v>0.688325</v>
+        <v>0.69345</v>
       </c>
       <c r="AT2" t="n">
         <v>0</v>
@@ -3766,31 +3766,31 @@
         <v>0</v>
       </c>
       <c r="AX2" t="n">
-        <v>43250684</v>
+        <v>57260916</v>
       </c>
       <c r="AY2" t="n">
         <v>0.17417</v>
       </c>
       <c r="AZ2" t="n">
-        <v>105442197</v>
+        <v>105353263</v>
       </c>
       <c r="BA2" t="n">
-        <v>121828073</v>
+        <v>121453187</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.07337</v>
+        <v>0.07432</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.82745004</v>
+        <v>0.83</v>
       </c>
       <c r="BD2" t="n">
-        <v>121828073</v>
+        <v>121453187</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.7401712</v>
+        <v>0.7392371</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.85115445</v>
+        <v>1.0077957</v>
       </c>
       <c r="BG2" t="n">
         <v>1767139200</v>
@@ -3808,16 +3808,16 @@
         <v>-0.02</v>
       </c>
       <c r="BL2" t="n">
-        <v>1.23</v>
+        <v>1.628</v>
       </c>
       <c r="BM2" t="n">
-        <v>8.238</v>
+        <v>10.907</v>
       </c>
       <c r="BN2" t="n">
-        <v>0</v>
+        <v>0.29565215</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.27449715</v>
+        <v>0.24487448</v>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
@@ -3825,7 +3825,7 @@
         </is>
       </c>
       <c r="BQ2" t="n">
-        <v>0.63</v>
+        <v>0.745</v>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
@@ -3926,144 +3926,144 @@
       </c>
       <c r="CS2" t="inlineStr">
         <is>
+          <t>Venture Life Group PLC        R</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>PREPRE</t>
+        </is>
+      </c>
+      <c r="CU2" t="n">
+        <v>0</v>
+      </c>
+      <c r="CV2" t="n">
+        <v>0.745</v>
+      </c>
+      <c r="CW2" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="CX2" t="n">
+        <v>1782134702</v>
+      </c>
+      <c r="CY2" t="inlineStr">
+        <is>
+          <t>FRA</t>
+        </is>
+      </c>
+      <c r="CZ2" t="inlineStr">
+        <is>
+          <t>finmb_252796646</t>
+        </is>
+      </c>
+      <c r="DA2" t="inlineStr">
+        <is>
+          <t>Europe/Berlin</t>
+        </is>
+      </c>
+      <c r="DB2" t="inlineStr">
+        <is>
+          <t>CEST</t>
+        </is>
+      </c>
+      <c r="DC2" t="n">
+        <v>7200000</v>
+      </c>
+      <c r="DD2" t="inlineStr">
+        <is>
+          <t>dr_market</t>
+        </is>
+      </c>
+      <c r="DE2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DF2" t="inlineStr">
+        <is>
+          <t>Venture Life Group plc</t>
+        </is>
+      </c>
+      <c r="DG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DH2" t="b">
+        <v>0</v>
+      </c>
+      <c r="DI2" t="n">
+        <v>1613458800000</v>
+      </c>
+      <c r="DJ2" t="n">
+        <v>0</v>
+      </c>
+      <c r="DK2" t="inlineStr">
+        <is>
+          <t>0.725 - 0.745</t>
+        </is>
+      </c>
+      <c r="DL2" t="inlineStr">
+        <is>
           <t>Frankfurt</t>
         </is>
       </c>
-      <c r="CT2" t="n">
-        <v>75</v>
-      </c>
-      <c r="CU2" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="CV2" t="n">
-        <v>1780406702</v>
-      </c>
-      <c r="CW2" t="inlineStr">
-        <is>
-          <t>FRA</t>
-        </is>
-      </c>
-      <c r="CX2" t="inlineStr">
-        <is>
-          <t>finmb_252796646</t>
-        </is>
-      </c>
-      <c r="CY2" t="inlineStr">
-        <is>
-          <t>Europe/Berlin</t>
-        </is>
-      </c>
-      <c r="CZ2" t="inlineStr">
-        <is>
-          <t>CEST</t>
-        </is>
-      </c>
-      <c r="DA2" t="n">
-        <v>7200000</v>
-      </c>
-      <c r="DB2" t="inlineStr">
-        <is>
-          <t>dr_market</t>
-        </is>
-      </c>
-      <c r="DC2" t="b">
+      <c r="DM2" t="n">
+        <v>238</v>
+      </c>
+      <c r="DN2" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="DO2" t="n">
+        <v>0.34234235</v>
+      </c>
+      <c r="DP2" t="inlineStr">
+        <is>
+          <t>0.555 - 0.82</t>
+        </is>
+      </c>
+      <c r="DQ2" t="n">
+        <v>-0.07499999</v>
+      </c>
+      <c r="DR2" t="n">
+        <v>-0.0914634</v>
+      </c>
+      <c r="DS2" t="n">
+        <v>29.565216</v>
+      </c>
+      <c r="DT2" t="n">
+        <v>1750318200</v>
+      </c>
+      <c r="DU2" t="n">
+        <v>1750318200</v>
+      </c>
+      <c r="DV2" t="n">
+        <v>1727874000</v>
+      </c>
+      <c r="DW2" t="n">
+        <v>1727874000</v>
+      </c>
+      <c r="DX2" t="b">
         <v>0</v>
       </c>
-      <c r="DD2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DE2" t="n">
-        <v>0.63</v>
-      </c>
-      <c r="DF2" t="inlineStr">
-        <is>
-          <t>PREPRE</t>
-        </is>
-      </c>
-      <c r="DG2" t="inlineStr">
-        <is>
-          <t>Venture Life Group PLC        R</t>
-        </is>
-      </c>
-      <c r="DH2" t="inlineStr">
-        <is>
-          <t>Venture Life Group plc</t>
-        </is>
-      </c>
-      <c r="DI2" t="n">
-        <v>0.07499999</v>
-      </c>
-      <c r="DJ2" t="n">
-        <v>0.13513511</v>
-      </c>
-      <c r="DK2" t="inlineStr">
-        <is>
-          <t>0.555 - 0.82</t>
-        </is>
-      </c>
-      <c r="DL2" t="n">
-        <v>-0.19</v>
-      </c>
-      <c r="DM2" t="n">
-        <v>-0.23170732</v>
-      </c>
-      <c r="DN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="DO2" t="n">
-        <v>1750318200</v>
-      </c>
-      <c r="DP2" t="n">
-        <v>1750318200</v>
-      </c>
-      <c r="DQ2" t="n">
-        <v>1727874000</v>
-      </c>
-      <c r="DR2" t="n">
-        <v>1727874000</v>
-      </c>
-      <c r="DS2" t="b">
-        <v>0</v>
-      </c>
-      <c r="DT2" t="n">
+      <c r="DY2" t="n">
         <v>-0.02</v>
       </c>
-      <c r="DU2" t="n">
-        <v>-0.04940003</v>
-      </c>
-      <c r="DV2" t="n">
-        <v>-0.07271126</v>
-      </c>
-      <c r="DW2" t="n">
-        <v>-0.058324993</v>
-      </c>
-      <c r="DX2" t="n">
-        <v>-0.08473467</v>
-      </c>
-      <c r="DY2" t="n">
+      <c r="DZ2" t="n">
+        <v>0.06520003000000001</v>
+      </c>
+      <c r="EA2" t="n">
+        <v>0.09591060999999999</v>
+      </c>
+      <c r="EB2" t="n">
+        <v>0.05155003</v>
+      </c>
+      <c r="EC2" t="n">
+        <v>0.0743385</v>
+      </c>
+      <c r="ED2" t="n">
         <v>15</v>
       </c>
-      <c r="DZ2" t="n">
+      <c r="EE2" t="n">
         <v>15</v>
-      </c>
-      <c r="EA2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EB2" t="b">
-        <v>0</v>
-      </c>
-      <c r="EC2" t="n">
-        <v>1613458800000</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>0</v>
-      </c>
-      <c r="EE2" t="inlineStr">
-        <is>
-          <t>0.62 - 0.63</t>
-        </is>
       </c>
       <c r="EF2" t="inlineStr"/>
     </row>
